--- a/ig/DM-OCTOBRE-2024/ValueSet-JDV-J41-TypeHoraire-ROR.xlsx
+++ b/ig/DM-OCTOBRE-2024/ValueSet-JDV-J41-TypeHoraire-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240628120000</t>
+    <t>20241025120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-28T12:00:00+01:00</t>
+    <t>2024-10-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -132,7 +132,7 @@
     <t>05</t>
   </si>
   <si>
-    <t>Horaire de visite d'un acteur de santé</t>
+    <t>Horaire de visite à domicile</t>
   </si>
   <si>
     <t>06</t>
@@ -157,6 +157,18 @@
   </si>
   <si>
     <t>Horaire à préciser</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Horaire de téléconsultation</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Horaire mixte : consultation ou téléconsultation</t>
   </si>
   <si>
     <t/>
@@ -435,7 +447,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -527,15 +539,31 @@
         <v>48</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
